--- a/Result/profitability/3530.xlsx
+++ b/Result/profitability/3530.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04499999999999998</v>
+        <v>-0.0275</v>
       </c>
       <c r="N2" t="n">
-        <v>16.26875</v>
+        <v>14.87375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.74</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2</v>
+        <v>0.165</v>
       </c>
       <c r="N3" t="n">
-        <v>12.3125</v>
+        <v>19.7975</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02749999999999996</v>
+        <v>0.08750000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>18.11</v>
+        <v>17.87625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.87</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.10125</v>
+        <v>0.03375</v>
       </c>
       <c r="N5" t="n">
-        <v>16.20375</v>
+        <v>16.54875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08375000000000003</v>
+        <v>-0.0975</v>
       </c>
       <c r="N6" t="n">
-        <v>16.0625</v>
+        <v>15.6825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.18</v>
+        <v>-0.26</v>
       </c>
       <c r="N7" t="n">
-        <v>14.67625</v>
+        <v>13.675</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -7540,6 +7540,133 @@
       </c>
       <c r="AM56" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>598</v>
+      </c>
+      <c r="D57" t="n">
+        <v>455</v>
+      </c>
+      <c r="E57" t="n">
+        <v>143</v>
+      </c>
+      <c r="F57" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="G57" t="n">
+        <v>54</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>8.95%</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>58</v>
+      </c>
+      <c r="K57" t="n">
+        <v>49</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.22125</v>
+      </c>
+      <c r="N57" t="n">
+        <v>18.67625</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>3.469999999999999</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.1695992179863146</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-2.454545454545455</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2.759999999999998</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.1303731695795936</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
